--- a/artfynd/S 1319-2026 artfynd.xlsx
+++ b/artfynd/S 1319-2026 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136480988</v>
       </c>
       <c r="B11" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1319-2026 artfynd.xlsx
+++ b/artfynd/S 1319-2026 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136480988</v>
       </c>
       <c r="B11" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1319-2026 artfynd.xlsx
+++ b/artfynd/S 1319-2026 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136480988</v>
       </c>
       <c r="B11" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1319-2026 artfynd.xlsx
+++ b/artfynd/S 1319-2026 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136480988</v>
       </c>
       <c r="B11" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1319-2026 artfynd.xlsx
+++ b/artfynd/S 1319-2026 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136480988</v>
       </c>
       <c r="B11" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
